--- a/24_DS_US_Canada_1/Attendance.xlsx
+++ b/24_DS_US_Canada_1/Attendance.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\24_DS_US_Canada_1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EE8C1D2-B053-44B2-AC84-16056E5667E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD7053E6-4274-466C-B2DD-920B5889A7FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="14">
   <si>
     <t>Neel</t>
   </si>
@@ -52,6 +52,21 @@
   </si>
   <si>
     <t>A</t>
+  </si>
+  <si>
+    <t>Sanghvi</t>
+  </si>
+  <si>
+    <t>Patel</t>
+  </si>
+  <si>
+    <t>Surani</t>
+  </si>
+  <si>
+    <t>First Name</t>
+  </si>
+  <si>
+    <t>Last Name</t>
   </si>
 </sst>
 </file>
@@ -370,75 +385,184 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.6640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" s="1">
+        <v>45601</v>
+      </c>
+      <c r="D1" s="1">
+        <v>45607</v>
+      </c>
       <c r="E1" s="1">
-        <v>45607</v>
+        <v>45608</v>
       </c>
       <c r="F1" s="1">
-        <v>45608</v>
+        <v>45614</v>
+      </c>
+      <c r="G1" s="1">
+        <v>45615</v>
+      </c>
+      <c r="H1" s="1">
+        <v>45621</v>
+      </c>
+      <c r="I1" s="1">
+        <v>45622</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" t="s">
+        <v>7</v>
+      </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
       <c r="B3" t="s">
         <v>5</v>
       </c>
+      <c r="C3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" t="s">
+        <v>7</v>
+      </c>
       <c r="E3" t="s">
         <v>7</v>
       </c>
       <c r="F3" t="s">
         <v>7</v>
       </c>
+      <c r="G3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>1</v>
       </c>
       <c r="B4" t="s">
         <v>6</v>
       </c>
+      <c r="C4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" t="s">
+        <v>7</v>
+      </c>
       <c r="E4" t="s">
         <v>7</v>
       </c>
       <c r="F4" t="s">
         <v>7</v>
       </c>
+      <c r="G4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>2</v>
       </c>
+      <c r="B5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" t="s">
+        <v>8</v>
+      </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
         <v>8</v>
       </c>
+      <c r="G5" t="s">
+        <v>8</v>
+      </c>
+      <c r="H5" t="s">
+        <v>7</v>
+      </c>
+      <c r="I5" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
+      <c r="B6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" t="s">
+        <v>8</v>
+      </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
+        <v>8</v>
+      </c>
+      <c r="G6" t="s">
+        <v>8</v>
+      </c>
+      <c r="H6" t="s">
+        <v>8</v>
+      </c>
+      <c r="I6" t="s">
         <v>8</v>
       </c>
     </row>

--- a/24_DS_US_Canada_1/Attendance.xlsx
+++ b/24_DS_US_Canada_1/Attendance.xlsx
@@ -8,14 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\24_DS_US_Canada_1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD7053E6-4274-466C-B2DD-920B5889A7FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1052C13E-9076-498A-917E-61EFC4C2602B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Attendance" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="18">
   <si>
     <t>Neel</t>
   </si>
@@ -67,6 +69,18 @@
   </si>
   <si>
     <t>Last Name</t>
+  </si>
+  <si>
+    <t>Present Online</t>
+  </si>
+  <si>
+    <t>Present Offline</t>
+  </si>
+  <si>
+    <t>Absent</t>
+  </si>
+  <si>
+    <t>Total</t>
   </si>
 </sst>
 </file>
@@ -385,14 +399,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.77734375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>12</v>
       </c>
@@ -420,8 +434,11 @@
       <c r="I1" s="1">
         <v>45622</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J1" s="1">
+        <v>45628</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -449,8 +466,11 @@
       <c r="I2" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -478,8 +498,11 @@
       <c r="I3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>1</v>
       </c>
@@ -507,8 +530,11 @@
       <c r="I4" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>2</v>
       </c>
@@ -536,8 +562,11 @@
       <c r="I5" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -564,6 +593,416 @@
       </c>
       <c r="I6" t="s">
         <v>8</v>
+      </c>
+      <c r="J6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6B5E99B-B435-460B-A67B-0A2B6AD6A37D}">
+  <dimension ref="A1:F13"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9.77734375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="1">
+        <v>45601</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="1">
+        <v>45607</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="1">
+        <v>45608</v>
+      </c>
+      <c r="B5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="1">
+        <v>45614</v>
+      </c>
+      <c r="B6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="1">
+        <v>45615</v>
+      </c>
+      <c r="B7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="1">
+        <v>45621</v>
+      </c>
+      <c r="B8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E8" t="s">
+        <v>7</v>
+      </c>
+      <c r="F8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="1">
+        <v>45622</v>
+      </c>
+      <c r="B9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" t="s">
+        <v>7</v>
+      </c>
+      <c r="E9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="1"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="1">
+        <v>45628</v>
+      </c>
+      <c r="B11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" t="s">
+        <v>7</v>
+      </c>
+      <c r="E11" t="s">
+        <v>7</v>
+      </c>
+      <c r="F11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="1">
+        <v>45629</v>
+      </c>
+      <c r="B12" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" t="s">
+        <v>7</v>
+      </c>
+      <c r="E12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" s="1">
+        <v>45635</v>
+      </c>
+      <c r="B13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E13" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" t="s">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A29799C-6D19-4017-B457-BF5CE267A922}">
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="8.5546875" customWidth="1"/>
+    <col min="3" max="3" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.21875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.21875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2">
+        <f>COUNTIF(Sheet2!$B$3:$B$9, "O")</f>
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <f>COUNTIF(Sheet2!$B$3:$B$9, "P")</f>
+        <v>4</v>
+      </c>
+      <c r="E2">
+        <f>COUNTIF(Sheet2!$B$3:$B$9, "A")</f>
+        <v>3</v>
+      </c>
+      <c r="F2">
+        <f>SUM(C2:E2)</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3">
+        <f>COUNTIF(Sheet2!$C$3:$C$9, "O")</f>
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <f>COUNTIF(Sheet2!$C$3:$C$9, "P")</f>
+        <v>7</v>
+      </c>
+      <c r="E3">
+        <f>COUNTIF(Sheet2!$C$3:$C$9, "A")</f>
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <f t="shared" ref="F3:F6" si="0">SUM(C3:E3)</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4">
+        <f>COUNTIF(Sheet2!$D$3:$D$9, "O")</f>
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <f>COUNTIF(Sheet2!$D$3:$D$9, "P")</f>
+        <v>7</v>
+      </c>
+      <c r="E4">
+        <f>COUNTIF(Sheet2!$D$3:$D$9, "A")</f>
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5">
+        <f>COUNTIF(Sheet2!$E$3:$E$9, "O")</f>
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <f>COUNTIF(Sheet2!$E$3:$E$9, "P")</f>
+        <v>2</v>
+      </c>
+      <c r="E5">
+        <f>COUNTIF(Sheet2!$E$3:$E$9, "A")</f>
+        <v>5</v>
+      </c>
+      <c r="F5">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6">
+        <f>COUNTIF(Sheet2!$F$3:$F$9, "O")</f>
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <f>COUNTIF(Sheet2!$F$3:$F$9, "P")</f>
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <f>COUNTIF(Sheet2!$F$3:$F$9, "A")</f>
+        <v>6</v>
+      </c>
+      <c r="F6">
+        <f t="shared" si="0"/>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/24_DS_US_Canada_1/Attendance.xlsx
+++ b/24_DS_US_Canada_1/Attendance.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28227"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\24_DS_US_Canada_1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1052C13E-9076-498A-917E-61EFC4C2602B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF3702EB-A666-4DA0-B8DB-8A93E5B5D4E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="19">
   <si>
     <t>Neel</t>
   </si>
@@ -81,6 +81,9 @@
   </si>
   <si>
     <t>Total</t>
+  </si>
+  <si>
+    <t>Removed</t>
   </si>
 </sst>
 </file>
@@ -605,7 +608,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6B5E99B-B435-460B-A67B-0A2B6AD6A37D}">
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.77734375" bestFit="1" customWidth="1"/>
@@ -851,6 +854,77 @@
         <v>8</v>
       </c>
       <c r="F13" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" s="1">
+        <v>45636</v>
+      </c>
+      <c r="B14" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F14" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="1">
+        <v>45642</v>
+      </c>
+      <c r="B15" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" t="s">
+        <v>7</v>
+      </c>
+      <c r="D15" t="s">
+        <v>7</v>
+      </c>
+      <c r="F15" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" s="1">
+        <v>45643</v>
+      </c>
+      <c r="B16" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" t="s">
+        <v>7</v>
+      </c>
+      <c r="D16" t="s">
+        <v>7</v>
+      </c>
+      <c r="F16" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" s="1">
+        <v>45649</v>
+      </c>
+      <c r="B17" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" t="s">
+        <v>7</v>
+      </c>
+      <c r="D17" t="s">
+        <v>7</v>
+      </c>
+      <c r="F17" t="s">
         <v>8</v>
       </c>
     </row>

--- a/24_DS_US_Canada_1/Attendance.xlsx
+++ b/24_DS_US_Canada_1/Attendance.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28324"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\24_DS_US_Canada_1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF3702EB-A666-4DA0-B8DB-8A93E5B5D4E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7236A944-0DC1-42EC-BFBE-7FE9BE390EBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="19">
   <si>
     <t>Neel</t>
   </si>
@@ -608,7 +608,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6B5E99B-B435-460B-A67B-0A2B6AD6A37D}">
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.77734375" bestFit="1" customWidth="1"/>
@@ -628,10 +628,10 @@
         <v>1</v>
       </c>
       <c r="E1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" t="s">
         <v>2</v>
-      </c>
-      <c r="F1" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
@@ -648,10 +648,10 @@
         <v>6</v>
       </c>
       <c r="E2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" t="s">
         <v>10</v>
-      </c>
-      <c r="F2" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
@@ -768,10 +768,10 @@
         <v>7</v>
       </c>
       <c r="E8" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -811,10 +811,10 @@
         <v>7</v>
       </c>
       <c r="E11" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
@@ -871,10 +871,10 @@
         <v>7</v>
       </c>
       <c r="E14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" t="s">
         <v>18</v>
-      </c>
-      <c r="F14" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
@@ -890,7 +890,7 @@
       <c r="D15" t="s">
         <v>7</v>
       </c>
-      <c r="F15" t="s">
+      <c r="E15" t="s">
         <v>8</v>
       </c>
     </row>
@@ -907,11 +907,11 @@
       <c r="D16" t="s">
         <v>7</v>
       </c>
-      <c r="F16" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E16" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>45649</v>
       </c>
@@ -924,7 +924,92 @@
       <c r="D17" t="s">
         <v>7</v>
       </c>
-      <c r="F17" t="s">
+      <c r="E17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="1">
+        <v>46021</v>
+      </c>
+      <c r="B18" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" t="s">
+        <v>7</v>
+      </c>
+      <c r="D18" t="s">
+        <v>8</v>
+      </c>
+      <c r="E18" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" s="1">
+        <v>45663</v>
+      </c>
+      <c r="B20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="1">
+        <v>45664</v>
+      </c>
+      <c r="B21" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" t="s">
+        <v>7</v>
+      </c>
+      <c r="E21" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" s="1">
+        <v>45677</v>
+      </c>
+      <c r="B22" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" t="s">
+        <v>7</v>
+      </c>
+      <c r="D22" t="s">
+        <v>7</v>
+      </c>
+      <c r="E22" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="1">
+        <v>45678</v>
+      </c>
+      <c r="B23" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" t="s">
+        <v>7</v>
+      </c>
+      <c r="D23" t="s">
+        <v>8</v>
+      </c>
+      <c r="E23" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1039,15 +1124,15 @@
         <v>10</v>
       </c>
       <c r="C5">
-        <f>COUNTIF(Sheet2!$E$3:$E$9, "O")</f>
+        <f>COUNTIF(Sheet2!$F$3:$F$9, "O")</f>
         <v>0</v>
       </c>
       <c r="D5">
-        <f>COUNTIF(Sheet2!$E$3:$E$9, "P")</f>
+        <f>COUNTIF(Sheet2!$F$3:$F$9, "P")</f>
         <v>2</v>
       </c>
       <c r="E5">
-        <f>COUNTIF(Sheet2!$E$3:$E$9, "A")</f>
+        <f>COUNTIF(Sheet2!$F$3:$F$9, "A")</f>
         <v>5</v>
       </c>
       <c r="F5">
@@ -1063,15 +1148,15 @@
         <v>9</v>
       </c>
       <c r="C6">
-        <f>COUNTIF(Sheet2!$F$3:$F$9, "O")</f>
+        <f>COUNTIF(Sheet2!$E$3:$E$9, "O")</f>
         <v>0</v>
       </c>
       <c r="D6">
-        <f>COUNTIF(Sheet2!$F$3:$F$9, "P")</f>
+        <f>COUNTIF(Sheet2!$E$3:$E$9, "P")</f>
         <v>1</v>
       </c>
       <c r="E6">
-        <f>COUNTIF(Sheet2!$F$3:$F$9, "A")</f>
+        <f>COUNTIF(Sheet2!$E$3:$E$9, "A")</f>
         <v>6</v>
       </c>
       <c r="F6">

--- a/24_DS_US_Canada_1/Attendance.xlsx
+++ b/24_DS_US_Canada_1/Attendance.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\24_DS_US_Canada_1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7236A944-0DC1-42EC-BFBE-7FE9BE390EBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DC3ED3A-631F-4548-9995-5AB7EA683AD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="19">
   <si>
     <t>Neel</t>
   </si>
@@ -608,7 +608,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6B5E99B-B435-460B-A67B-0A2B6AD6A37D}">
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.77734375" bestFit="1" customWidth="1"/>
@@ -1010,6 +1010,23 @@
         <v>8</v>
       </c>
       <c r="E23" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24" s="1">
+        <v>45685</v>
+      </c>
+      <c r="B24" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" t="s">
+        <v>7</v>
+      </c>
+      <c r="D24" t="s">
+        <v>7</v>
+      </c>
+      <c r="E24" t="s">
         <v>8</v>
       </c>
     </row>

--- a/24_DS_US_Canada_1/Attendance.xlsx
+++ b/24_DS_US_Canada_1/Attendance.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\24_DS_US_Canada_1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DC3ED3A-631F-4548-9995-5AB7EA683AD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F8BCAD5-447B-4948-BFC5-1C4BA02DD9D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="19">
   <si>
     <t>Neel</t>
   </si>
@@ -608,7 +608,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6B5E99B-B435-460B-A67B-0A2B6AD6A37D}">
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.77734375" bestFit="1" customWidth="1"/>
@@ -1027,6 +1027,40 @@
         <v>7</v>
       </c>
       <c r="E24" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26" s="1">
+        <v>45698</v>
+      </c>
+      <c r="B26" t="s">
+        <v>8</v>
+      </c>
+      <c r="C26" t="s">
+        <v>8</v>
+      </c>
+      <c r="D26" t="s">
+        <v>8</v>
+      </c>
+      <c r="E26" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A27" s="1">
+        <v>45699</v>
+      </c>
+      <c r="B27" t="s">
+        <v>8</v>
+      </c>
+      <c r="C27" t="s">
+        <v>7</v>
+      </c>
+      <c r="D27" t="s">
+        <v>8</v>
+      </c>
+      <c r="E27" t="s">
         <v>8</v>
       </c>
     </row>

--- a/24_DS_US_Canada_1/Attendance.xlsx
+++ b/24_DS_US_Canada_1/Attendance.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\24_DS_US_Canada_1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F8BCAD5-447B-4948-BFC5-1C4BA02DD9D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EEDF3CA-461C-4EF3-B93F-5BF9366B2B93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="20">
   <si>
     <t>Neel</t>
   </si>
@@ -84,6 +84,9 @@
   </si>
   <si>
     <t>Removed</t>
+  </si>
+  <si>
+    <t>Left</t>
   </si>
 </sst>
 </file>
@@ -608,7 +611,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6B5E99B-B435-460B-A67B-0A2B6AD6A37D}">
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.77734375" bestFit="1" customWidth="1"/>
@@ -625,10 +628,10 @@
         <v>4</v>
       </c>
       <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
         <v>1</v>
-      </c>
-      <c r="E1" t="s">
-        <v>3</v>
       </c>
       <c r="F1" t="s">
         <v>2</v>
@@ -645,10 +648,10 @@
         <v>5</v>
       </c>
       <c r="D2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" t="s">
         <v>6</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
       </c>
       <c r="F2" t="s">
         <v>10</v>
@@ -685,10 +688,10 @@
         <v>7</v>
       </c>
       <c r="D4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
         <v>8</v>
@@ -705,10 +708,10 @@
         <v>7</v>
       </c>
       <c r="D5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F5" t="s">
         <v>8</v>
@@ -725,10 +728,10 @@
         <v>7</v>
       </c>
       <c r="D6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F6" t="s">
         <v>8</v>
@@ -745,10 +748,10 @@
         <v>7</v>
       </c>
       <c r="D7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F7" t="s">
         <v>8</v>
@@ -765,10 +768,10 @@
         <v>7</v>
       </c>
       <c r="D8" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E8" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F8" t="s">
         <v>7</v>
@@ -785,10 +788,10 @@
         <v>7</v>
       </c>
       <c r="D9" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E9" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F9" t="s">
         <v>8</v>
@@ -808,10 +811,10 @@
         <v>7</v>
       </c>
       <c r="D11" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E11" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F11" t="s">
         <v>7</v>
@@ -828,10 +831,10 @@
         <v>7</v>
       </c>
       <c r="D12" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F12" t="s">
         <v>8</v>
@@ -848,10 +851,10 @@
         <v>7</v>
       </c>
       <c r="D13" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E13" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F13" t="s">
         <v>8</v>
@@ -868,10 +871,10 @@
         <v>7</v>
       </c>
       <c r="D14" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E14" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F14" t="s">
         <v>18</v>
@@ -888,10 +891,10 @@
         <v>7</v>
       </c>
       <c r="D15" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E15" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
@@ -905,10 +908,10 @@
         <v>7</v>
       </c>
       <c r="D16" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E16" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
@@ -922,10 +925,10 @@
         <v>7</v>
       </c>
       <c r="D17" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E17" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
@@ -973,10 +976,10 @@
         <v>8</v>
       </c>
       <c r="D21" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E21" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
@@ -990,10 +993,10 @@
         <v>7</v>
       </c>
       <c r="D22" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E22" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
@@ -1024,10 +1027,10 @@
         <v>7</v>
       </c>
       <c r="D24" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E24" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
@@ -1041,10 +1044,10 @@
         <v>8</v>
       </c>
       <c r="D26" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E26" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
@@ -1060,7 +1063,32 @@
       <c r="D27" t="s">
         <v>8</v>
       </c>
-      <c r="E27" t="s">
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A28" s="1">
+        <v>45705</v>
+      </c>
+      <c r="B28" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" t="s">
+        <v>7</v>
+      </c>
+      <c r="D28" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A29" s="1">
+        <v>45706</v>
+      </c>
+      <c r="B29" t="s">
+        <v>8</v>
+      </c>
+      <c r="C29" t="s">
+        <v>7</v>
+      </c>
+      <c r="D29" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1151,15 +1179,15 @@
         <v>6</v>
       </c>
       <c r="C4">
-        <f>COUNTIF(Sheet2!$D$3:$D$9, "O")</f>
+        <f>COUNTIF(Sheet2!$E$3:$E$9, "O")</f>
         <v>0</v>
       </c>
       <c r="D4">
-        <f>COUNTIF(Sheet2!$D$3:$D$9, "P")</f>
+        <f>COUNTIF(Sheet2!$E$3:$E$9, "P")</f>
         <v>7</v>
       </c>
       <c r="E4">
-        <f>COUNTIF(Sheet2!$D$3:$D$9, "A")</f>
+        <f>COUNTIF(Sheet2!$E$3:$E$9, "A")</f>
         <v>0</v>
       </c>
       <c r="F4">
@@ -1199,15 +1227,15 @@
         <v>9</v>
       </c>
       <c r="C6">
-        <f>COUNTIF(Sheet2!$E$3:$E$9, "O")</f>
+        <f>COUNTIF(Sheet2!$D$3:$D$9, "O")</f>
         <v>0</v>
       </c>
       <c r="D6">
-        <f>COUNTIF(Sheet2!$E$3:$E$9, "P")</f>
+        <f>COUNTIF(Sheet2!$D$3:$D$9, "P")</f>
         <v>1</v>
       </c>
       <c r="E6">
-        <f>COUNTIF(Sheet2!$E$3:$E$9, "A")</f>
+        <f>COUNTIF(Sheet2!$D$3:$D$9, "A")</f>
         <v>6</v>
       </c>
       <c r="F6">

--- a/24_DS_US_Canada_1/Attendance.xlsx
+++ b/24_DS_US_Canada_1/Attendance.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\24_DS_US_Canada_1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EEDF3CA-461C-4EF3-B93F-5BF9366B2B93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DD7F982-D069-4DE9-944C-54137F3D6BCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="20">
   <si>
     <t>Neel</t>
   </si>
@@ -611,7 +611,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6B5E99B-B435-460B-A67B-0A2B6AD6A37D}">
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.77734375" bestFit="1" customWidth="1"/>
@@ -1090,6 +1090,48 @@
       </c>
       <c r="D29" t="s">
         <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A30" s="1">
+        <v>45713</v>
+      </c>
+      <c r="B30" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30" t="s">
+        <v>7</v>
+      </c>
+      <c r="D30" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A32" s="1">
+        <v>45720</v>
+      </c>
+      <c r="B32" t="s">
+        <v>8</v>
+      </c>
+      <c r="C32" t="s">
+        <v>7</v>
+      </c>
+      <c r="D32" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A33" s="1">
+        <v>45726</v>
+      </c>
+      <c r="B33" t="s">
+        <v>7</v>
+      </c>
+      <c r="C33" t="s">
+        <v>7</v>
+      </c>
+      <c r="D33" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/24_DS_US_Canada_1/Attendance.xlsx
+++ b/24_DS_US_Canada_1/Attendance.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\24_DS_US_Canada_1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DD7F982-D069-4DE9-944C-54137F3D6BCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3495C3A2-3A81-4902-BCF2-5A22BAA77939}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="20">
   <si>
     <t>Neel</t>
   </si>
@@ -611,7 +611,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6B5E99B-B435-460B-A67B-0A2B6AD6A37D}">
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.77734375" bestFit="1" customWidth="1"/>
@@ -1132,6 +1132,48 @@
       </c>
       <c r="D33" t="s">
         <v>7</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A34" s="1">
+        <v>45727</v>
+      </c>
+      <c r="B34" t="s">
+        <v>8</v>
+      </c>
+      <c r="C34" t="s">
+        <v>7</v>
+      </c>
+      <c r="D34" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A35" s="1">
+        <v>45733</v>
+      </c>
+      <c r="B35" t="s">
+        <v>8</v>
+      </c>
+      <c r="C35" t="s">
+        <v>7</v>
+      </c>
+      <c r="D35" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A36" s="1">
+        <v>45741</v>
+      </c>
+      <c r="B36" t="s">
+        <v>8</v>
+      </c>
+      <c r="C36" t="s">
+        <v>7</v>
+      </c>
+      <c r="D36" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/24_DS_US_Canada_1/Attendance.xlsx
+++ b/24_DS_US_Canada_1/Attendance.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\24_DS_US_Canada_1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3495C3A2-3A81-4902-BCF2-5A22BAA77939}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EA4BE72-7072-430A-9068-C8AA3C856E38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="20">
   <si>
     <t>Neel</t>
   </si>
@@ -71,22 +71,22 @@
     <t>Last Name</t>
   </si>
   <si>
-    <t>Present Online</t>
-  </si>
-  <si>
     <t>Present Offline</t>
   </si>
   <si>
     <t>Absent</t>
   </si>
   <si>
-    <t>Total</t>
-  </si>
-  <si>
     <t>Removed</t>
   </si>
   <si>
     <t>Left</t>
+  </si>
+  <si>
+    <t>Total Lectures Taken</t>
+  </si>
+  <si>
+    <t>Presence %</t>
   </si>
 </sst>
 </file>
@@ -611,7 +611,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6B5E99B-B435-460B-A67B-0A2B6AD6A37D}">
-  <dimension ref="A1:F36"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.77734375" bestFit="1" customWidth="1"/>
@@ -877,7 +877,7 @@
         <v>7</v>
       </c>
       <c r="F14" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
@@ -1047,7 +1047,7 @@
         <v>7</v>
       </c>
       <c r="E26" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
@@ -1173,6 +1173,62 @@
         <v>7</v>
       </c>
       <c r="D36" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A37" s="1">
+        <v>45747</v>
+      </c>
+      <c r="B37" t="s">
+        <v>7</v>
+      </c>
+      <c r="C37" t="s">
+        <v>7</v>
+      </c>
+      <c r="D37" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A39" s="1">
+        <v>45748</v>
+      </c>
+      <c r="B39" t="s">
+        <v>8</v>
+      </c>
+      <c r="C39" t="s">
+        <v>7</v>
+      </c>
+      <c r="D39" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A40" s="1">
+        <v>45754</v>
+      </c>
+      <c r="B40" t="s">
+        <v>8</v>
+      </c>
+      <c r="C40" t="s">
+        <v>7</v>
+      </c>
+      <c r="D40" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A41" s="1">
+        <v>45755</v>
+      </c>
+      <c r="B41" t="s">
+        <v>8</v>
+      </c>
+      <c r="C41" t="s">
+        <v>7</v>
+      </c>
+      <c r="D41" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1183,28 +1239,28 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A29799C-6D19-4017-B457-BF5CE267A922}">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="8.5546875" customWidth="1"/>
-    <col min="3" max="3" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.21875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="6.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="C1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" t="s">
         <v>14</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>15</v>
       </c>
-      <c r="E1" t="s">
-        <v>16</v>
-      </c>
       <c r="F1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
@@ -1215,20 +1271,20 @@
         <v>11</v>
       </c>
       <c r="C2">
-        <f>COUNTIF(Sheet2!$B$3:$B$9, "O")</f>
-        <v>0</v>
+        <f>COUNTA(Sheet2!B:B) - 2</f>
+        <v>34</v>
       </c>
       <c r="D2">
-        <f>COUNTIF(Sheet2!$B$3:$B$9, "P")</f>
-        <v>4</v>
+        <f>COUNTIF(Sheet2!B:B, "P") + COUNTIF(Sheet2!B:B, "O")</f>
+        <v>13</v>
       </c>
       <c r="E2">
-        <f>COUNTIF(Sheet2!$B$3:$B$9, "A")</f>
-        <v>3</v>
+        <f>C2-D2</f>
+        <v>21</v>
       </c>
       <c r="F2">
-        <f>SUM(C2:E2)</f>
-        <v>7</v>
+        <f>ROUND(D2*100/C2, 0)</f>
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
@@ -1239,92 +1295,44 @@
         <v>5</v>
       </c>
       <c r="C3">
-        <f>COUNTIF(Sheet2!$C$3:$C$9, "O")</f>
-        <v>0</v>
+        <f>COUNTA(Sheet2!B:B) - 2</f>
+        <v>34</v>
       </c>
       <c r="D3">
-        <f>COUNTIF(Sheet2!$C$3:$C$9, "P")</f>
-        <v>7</v>
+        <f>COUNTIF(Sheet2!C:C, "P") + COUNTIF(Sheet2!C:C, "O")</f>
+        <v>32</v>
       </c>
       <c r="E3">
-        <f>COUNTIF(Sheet2!$C$3:$C$9, "A")</f>
-        <v>0</v>
+        <f t="shared" ref="E3:E4" si="0">C3-D3</f>
+        <v>2</v>
       </c>
       <c r="F3">
-        <f t="shared" ref="F3:F6" si="0">SUM(C3:E3)</f>
-        <v>7</v>
+        <f t="shared" ref="F3:F4" si="1">ROUND(D3*100/C3, 0)</f>
+        <v>94</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C4">
-        <f>COUNTIF(Sheet2!$E$3:$E$9, "O")</f>
-        <v>0</v>
+        <f>COUNTA(Sheet2!B:B) - 2</f>
+        <v>34</v>
       </c>
       <c r="D4">
-        <f>COUNTIF(Sheet2!$E$3:$E$9, "P")</f>
-        <v>7</v>
+        <f>COUNTIF(Sheet2!D:D, "P") + COUNTIF(Sheet2!D:D, "O")</f>
+        <v>4</v>
       </c>
       <c r="E4">
-        <f>COUNTIF(Sheet2!$E$3:$E$9, "A")</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>30</v>
       </c>
       <c r="F4">
-        <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>2</v>
-      </c>
-      <c r="B5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5">
-        <f>COUNTIF(Sheet2!$F$3:$F$9, "O")</f>
-        <v>0</v>
-      </c>
-      <c r="D5">
-        <f>COUNTIF(Sheet2!$F$3:$F$9, "P")</f>
-        <v>2</v>
-      </c>
-      <c r="E5">
-        <f>COUNTIF(Sheet2!$F$3:$F$9, "A")</f>
-        <v>5</v>
-      </c>
-      <c r="F5">
-        <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6">
-        <f>COUNTIF(Sheet2!$D$3:$D$9, "O")</f>
-        <v>0</v>
-      </c>
-      <c r="D6">
-        <f>COUNTIF(Sheet2!$D$3:$D$9, "P")</f>
-        <v>1</v>
-      </c>
-      <c r="E6">
-        <f>COUNTIF(Sheet2!$D$3:$D$9, "A")</f>
-        <v>6</v>
-      </c>
-      <c r="F6">
-        <f t="shared" si="0"/>
-        <v>7</v>
+        <f t="shared" si="1"/>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
